--- a/src/data/gary_inputs.xlsx
+++ b/src/data/gary_inputs.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1166,25 +1166,102 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ACIL Allen LNG price</t>
+          <t>LNG trains</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>export_headroom</t>
+          <t>lng_nameplate_tj_day</t>
         </is>
       </c>
       <c r="C30" t="n">
+        <v>3680</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TJ/day</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Total east coast liquefaction nameplate (100% utilisation). Mirrors lng_daily_target in lng_parameters.csv. This is the PHYSICAL ceiling on exports under netback pricing - a train cannot liquefy more than it can liquefy, however attractive the netback.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LNG trains</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>lng_train_shares</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>APLNG:0.357,GLNG:0.31,QCLNG:0.333</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>node:share</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Each train's share of nameplate. Mirrors the *_factor rows in lng_parameters.csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LNG trains</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>lng_foundation_share</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Share of planned export volume committed under long-term foundation SPAs: take-or-pay, therefore price-insensitive, served whatever the netback. The remainder is the uncontracted spot tail that bids at the netback and can be outbid by a domestic buyer or taken by a reservation. DERIVED FROM PUBLIC DATA: the ACCC publishes Queensland LNG producers' uncontracted gas each quarter and reported 22 PJ available for Q1 2026 (ACCC, east coast gas supply outlook, Q1 2026); against ~325-330 PJ of quarterly exports that is ~7% uncontracted, hence 0.93. Structure confirmed by ACIL Allen (14 Nov 2025) 2.3.2: 'the supply under foundation customers is untouched in our modelling, LNG exporters then supply the domestic market and export further gas via spot cargoes'. ONE QUARTER's figure, so treat as a KEY SENSITIVITY - it sets how much export volume is contestable at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Gas reservation</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>reservation_respects_contracts</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
         <v>1</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>multiple</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Ceiling on each train's liquefaction as a multiple of its planned export volume. 1.0 = exports may only be DECLINED, never expanded (default). Above 1.0 lets spare liquefaction absorb cheap gas, which is what makes the netback ANCHOR domestic prices rather than only cap them in scarcity - but GARY has no reserves constraint, so a high value lets exports soak up field deliverability indefinitely.</t>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1=yes, 0=no</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Default for whether a reservation may only take UNCONTRACTED export volume. 1: the reservation bites on the spot tail first and is capped at (1 - lng_foundation_share) of planned volume, so foundation SPAs are not broken - which is how the Heads of Agreement with the east coast LNG exporters actually works. 0: the reservation takes its share of ALL export volume, foundation contracts included. The dashboard toggle overrides this.</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1371,6 +1448,78 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Multiplier over the high window; 1.1 outside it</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LNG_Netback</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Accelerated</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Weak global LNG demand: ACIL Allen's Accelerated Transition price path (netback $7.33/GJ in 2030, $3.94 by 2050)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LNG_Netback</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>The run's own GSOO scenario price path</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LNG_Netback</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SlowerGrowth</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Strong global LNG demand: ACIL Allen's Slower Growth price path (netback $10.39/GJ in 2030, at the $12 Code cap from 2040)</t>
         </is>
       </c>
     </row>
